--- a/AAII_Financials/Quarterly/ANYYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANYYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
   <si>
     <t>ANYYY</t>
   </si>
@@ -656,83 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -775,8 +779,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -819,8 +826,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +873,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -881,8 +894,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -925,8 +939,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -969,8 +986,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1013,8 +1033,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1057,8 +1080,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,8 +1098,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1116,8 +1143,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1160,8 +1190,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1178,8 +1211,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1222,8 +1256,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1266,8 +1303,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1310,8 +1350,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1354,8 +1397,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1398,8 +1444,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1442,8 +1491,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1486,8 +1538,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1530,8 +1585,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1574,8 +1632,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1618,8 +1679,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1662,8 +1726,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1706,8 +1773,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1750,8 +1820,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1794,8 +1867,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1838,8 +1914,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1882,57 +1961,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1949,8 +2034,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1967,82 +2053,86 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1587200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3394800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2404200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1116100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2421400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1885600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1602800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2803100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2612100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1384200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2084900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1384200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2382800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1681700</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>510900</v>
+        <v>471200</v>
       </c>
       <c r="E42" s="3">
+        <v>499600</v>
+      </c>
+      <c r="F42" s="3">
         <v>486700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>65100</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>36200</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2053,318 +2143,342 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>33700</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1090700</v>
+      </c>
+      <c r="E43" s="3">
         <v>860400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1016900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1116400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>840200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>873600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1137100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>976400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1082100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>950100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>954500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>950100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>654600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>719800</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E44" s="3">
         <v>7400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7400</v>
-      </c>
-      <c r="O44" s="3">
-        <v>7000</v>
       </c>
       <c r="P44" s="3">
         <v>7000</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3">
         <v>73400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>64800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>71300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>44900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3164500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4773500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3915400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2313000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3332800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2902200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2777000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3817300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3737100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2386600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3089600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2386600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3081500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2442100</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>680300</v>
+      </c>
+      <c r="E47" s="3">
         <v>349700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>332700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>287200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>285100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>257700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>254700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>286300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>203600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>273700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>203400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>273700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>284900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14186300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13947400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14242900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14092000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12989300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12436400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12841400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12939000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13311300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13088100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12609600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13088100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13069400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12958600</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2455900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2180300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1996400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1859100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1665400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1559000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1698100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1844200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1904600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1701400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1660600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1701400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1600100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>862100</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2407,8 +2521,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2451,52 +2568,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>544800</v>
+      </c>
+      <c r="E52" s="3">
         <v>522300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>493700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>456200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>402700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>357700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>244000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>186600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>177100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>148000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>205500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>148000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>147700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2539,52 +2662,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21479700</v>
+      </c>
+      <c r="E54" s="3">
         <v>22131200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21360300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19399800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18729900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17872800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17869600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19132800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19405600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17869900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18035600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17869900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18454700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16938300</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2601,8 +2730,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2619,272 +2749,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1025100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1044100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>366600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1017200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>996300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>310500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>876800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>932900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>319400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>825000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>794500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>825000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1358600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>320900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1469100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1045800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1014500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>861400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1484000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1387900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2219600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1901000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1958500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1157700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1130400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1157700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1432400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>703700</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>313200</v>
+      </c>
+      <c r="E59" s="3">
         <v>216300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>563800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>314200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>197000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>471600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>233900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>140400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>569100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>214100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>380900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>214100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>119700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>548700</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2807500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2306200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2080800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2192800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2677300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2313300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3330200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2974400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2941600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2196800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2305800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2196800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2910600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1652300</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7800200</v>
+      </c>
+      <c r="E61" s="3">
         <v>8142500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7858000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7270000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6218200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6189400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6303700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7159500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7531500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7959700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7701100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7959700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7644900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7664000</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>274200</v>
+      </c>
+      <c r="E62" s="3">
         <v>253100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>247800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>197300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>183600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>167400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>144600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>124700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>121600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>75700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>73300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>75700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>75400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2927,8 +3076,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2971,8 +3123,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3015,52 +3170,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11358100</v>
+      </c>
+      <c r="E66" s="3">
         <v>11123000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10611700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10103800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9495100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9076700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10208200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10700200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11051300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10683600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10509600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10683600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11081300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9839400</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3077,8 +3238,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3121,8 +3283,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3165,8 +3330,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3209,8 +3377,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3253,52 +3424,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7127800</v>
+      </c>
+      <c r="E72" s="3">
         <v>8300700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8060900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6602400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6729600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6424800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5110500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5788200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5642000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4455400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4878300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4455400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4698600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4478400</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3341,8 +3518,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3385,8 +3565,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3429,52 +3612,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9884800</v>
+      </c>
+      <c r="E76" s="3">
         <v>11064800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10809500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9358600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9298900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8866700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7724700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8506800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8430800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7261300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7589500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7261300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7454100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7179200</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3517,57 +3706,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3610,8 +3805,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3628,52 +3826,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>225500</v>
+      </c>
+      <c r="E83" s="3">
         <v>89400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>227400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>228200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>141200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>221000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>215800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>143500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>195800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>206900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>195800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>206900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>217500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>156400</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3716,8 +3918,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3760,8 +3965,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3804,8 +4012,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3848,8 +4059,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3892,52 +4106,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>788400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1047400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>307500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>774000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>886800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>408100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>726200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>780700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>348800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>593500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>905800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>593500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>548400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>325800</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3954,52 +4174,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-191300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-228700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-257700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-222300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-184200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-181100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-203500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-250500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-129600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-149500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-122900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-149500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-189900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-106500</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4042,8 +4266,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4086,52 +4313,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-574900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-350200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-797400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-340100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-212900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-179900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-213900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-291200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-144600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-822300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-149000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-822300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-428300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-190800</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4148,52 +4381,56 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>1880900</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
         <v>26200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1732800</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>20300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1231100</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>13000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>777800</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>777800</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4236,8 +4473,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4280,8 +4520,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4324,136 +4567,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1993000</v>
+      </c>
+      <c r="E100" s="3">
         <v>325500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>844400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1940500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-227100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-576900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1673500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-231000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>232000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-778900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-778900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>538600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-140600</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-28000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-19900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1776600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1033800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>345900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1514900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>452900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-376600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1181000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>253600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>434700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1010100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>743000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1010100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>673200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9400</v>
       </c>
     </row>
